--- a/entregables/interfaces_graficas/diseno_interfaces_graficas_app_movil.xlsx
+++ b/entregables/interfaces_graficas/diseno_interfaces_graficas_app_movil.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7A2F89-A10A-4907-94C3-48F0AFC6AA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 Login" sheetId="1" r:id="rId1"/>
